--- a/doc/PatPet_테이블정의서.xlsx
+++ b/doc/PatPet_테이블정의서.xlsx
@@ -903,14 +903,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>[PetPulse] 데이터베이스 테이블 목록 (ERD Overview)</t>
+          <t>[PatPet] 데이터베이스 테이블 목록 (ERD Overview)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>■ 시스템명: PetPulse 반려동물 AI 헬스케어 | 작성일: 2026.08.07 | DBMS: Supabase PostgreSQL</t>
+          <t>■ 시스템명: PatPet 반려동물 AI 헬스케어 | 작성일: 2026.08.07 | DBMS: Supabase PostgreSQL</t>
         </is>
       </c>
     </row>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>PetPulse 반려동물 AI 헬스케어</t>
+          <t>PatPet 반려동물 AI 헬스케어</t>
         </is>
       </c>
       <c r="F3" s="15" t="n"/>
@@ -2074,7 +2074,7 @@
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>PetPulse 반려동물 AI 헬스케어</t>
+          <t>PatPet 반려동물 AI 헬스케어</t>
         </is>
       </c>
       <c r="F3" s="15" t="n"/>
@@ -2748,7 +2748,7 @@
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>PetPulse 반려동물 AI 헬스케어</t>
+          <t>PatPet 반려동물 AI 헬스케어</t>
         </is>
       </c>
       <c r="F3" s="15" t="n"/>
@@ -3422,7 +3422,7 @@
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>PetPulse 반려동물 AI 헬스케어</t>
+          <t>PatPet 반려동물 AI 헬스케어</t>
         </is>
       </c>
       <c r="F3" s="15" t="n"/>
@@ -4252,7 +4252,7 @@
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>PetPulse 반려동물 AI 헬스케어</t>
+          <t>PatPet 반려동물 AI 헬스케어</t>
         </is>
       </c>
       <c r="F3" s="15" t="n"/>
@@ -5078,7 +5078,7 @@
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>PetPulse 반려동물 AI 헬스케어</t>
+          <t>PatPet 반려동물 AI 헬스케어</t>
         </is>
       </c>
       <c r="F3" s="15" t="n"/>
@@ -5816,7 +5816,7 @@
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>PetPulse 반려동물 AI 헬스케어</t>
+          <t>PatPet 반려동물 AI 헬스케어</t>
         </is>
       </c>
       <c r="F3" s="15" t="n"/>
@@ -6762,7 +6762,7 @@
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>PetPulse 반려동물 AI 헬스케어</t>
+          <t>PatPet 반려동물 AI 헬스케어</t>
         </is>
       </c>
       <c r="F3" s="15" t="n"/>
@@ -7526,7 +7526,7 @@
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>PetPulse 반려동물 AI 헬스케어</t>
+          <t>PatPet 반려동물 AI 헬스케어</t>
         </is>
       </c>
       <c r="F3" s="15" t="n"/>
@@ -8282,7 +8282,7 @@
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>PetPulse 반려동물 AI 헬스케어</t>
+          <t>PatPet 반려동물 AI 헬스케어</t>
         </is>
       </c>
       <c r="F3" s="15" t="n"/>
@@ -9146,7 +9146,7 @@
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>PetPulse 반려동물 AI 헬스케어</t>
+          <t>PatPet 반려동물 AI 헬스케어</t>
         </is>
       </c>
       <c r="F3" s="15" t="n"/>
